--- a/장소.xlsx
+++ b/장소.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/terrykim/taiwan-tour/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C38B66-2A9F-534F-BDF6-61200E801928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C115BCC-9332-CA44-AA83-FA41DD8465D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2140" yWindow="2060" windowWidth="28040" windowHeight="17440" xr2:uid="{C2D92EBE-1494-AD41-8A5C-1CD3269D8E2F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="102">
   <si>
     <t>구</t>
   </si>
@@ -53,9 +53,6 @@
     <t>구글 맵 링크</t>
   </si>
   <si>
-    <t>숙소</t>
-  </si>
-  <si>
     <t>코지 호텔</t>
   </si>
   <si>
@@ -122,9 +119,6 @@
     <t>중산구</t>
   </si>
   <si>
-    <t xml:space="preserve">신트랜드 </t>
-  </si>
-  <si>
     <t>화산 1914 창의문화 원구</t>
   </si>
   <si>
@@ -252,9 +246,6 @@
   </si>
   <si>
     <t>타오위안</t>
-  </si>
-  <si>
-    <t>교통</t>
   </si>
   <si>
     <t>전자 입출국 삼일전!!!</t>
@@ -318,9 +309,6 @@
     <t>관광</t>
   </si>
   <si>
-    <t>음식</t>
-  </si>
-  <si>
     <t>스펀지 케익 緣味古早味現烤蛋糕</t>
   </si>
   <si>
@@ -331,6 +319,39 @@
   </si>
   <si>
     <t>https://maps.app.goo.gl/41ew7G14UMgrGkHy8</t>
+  </si>
+  <si>
+    <t>신트랜드</t>
+  </si>
+  <si>
+    <t>먹거리</t>
+  </si>
+  <si>
+    <t>호텔/교통</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ba+Fang+Yun+Ji+Dumpling/@25.0468618,121.4945876,13.83z/data=!4m10!1m2!2m1!1z5YWr5pa55LqR6ZuG6ZSF6LS05rC06aW65LiT5Y2W5bqXIOael-ajrg!3m6!1s0x3442a967df555e03:0xf872acef8f693944!8m2!3d25.0550599!4d121.5255828!15sCijlhavmlrnkupHpm4bplIXotLTmsLTppbrkuJPljZblupcg5p6X5qOuIgOIAQFaMCIu5YWr5pa5IOS6kembhiDplIXotLQg5rC06aW6IOS4k-WNliDlupcg5p6XIOajrpIBE2R1bXBsaW5nX3Jlc3RhdXJhbnSaASRDaGREU1VoTk1HOW5TMFZKUTBGblNVTkNMVFZFZDJwUlJSQULgAQD6AQQIABAb!16s%2Fg%2F11cn0r_jlg?entry=ttu&amp;g_ep=EgoyMDI2MDMxMS4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>팔방운집 궈테 군만두</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/%E5%8F%B0%E7%81%A3%E7%AC%AC%E4%B8%80%E5%AE%B6%E7%87%92%E7%83%A4%E9%B9%BD%E9%85%A5%E9%9B%9E/@25.057468,121.5232269,14.78z/data=!4m10!1m2!2m1!1z5Y-w5rm-55uQ6YWl6bih!3m6!1s0x3442a95c5bef03fb:0x919c6e4adf4fb617!8m2!3d25.0594813!4d121.5288503!15sCg_lj7Dmub7nm5DphaXpuKFaFCIS5Y-w5rm-IOebkCDphaUg6bihkgEEZGVsaZoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VNeExWQjZhSEozUlJBQuABAPoBBAgAEB0!16s%2Fg%2F11bw_6g6xb?entry=ttu&amp;g_ep=EgoyMDI2MDMxMS4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>옌수지 튀김 (쓰윈)</t>
+  </si>
+  <si>
+    <t>옌수지 튀김 (타이완)</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Shi+Yun+Crispy+Salted+Fried+Chicken+(Ximen)/@25.0424874,121.4685774,14z/data=!4m10!1m2!2m1!1sSHI+YUN+Taiwanese+Fried+Chicken!3m6!1s0x3442a93a5efb2fc7:0x28923df0126c4706!8m2!3d25.0424871!4d121.5066831!15sCh9TSEkgWVVOIFRhaXdhbmVzZSBGcmllZCBDaGlja2VuWiEiH3NoaSB5dW4gdGFpd2FuZXNlIGZyaWVkIGNoaWNrZW6SARJza2V3ZXJfZGVlcF9mcnlpbmeaASNDaFpEU1VoTk1HOW5TMFZKUTBGblNVUmFkVXREYkZGUkVBReABAPoBBAgAEEs!16s%2Fg%2F11h4v7khv7?entry=ttu&amp;g_ep=EgoyMDI2MDMxMS4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>츠펑 MZ 감성 거리</t>
+  </si>
+  <si>
+    <t>http://google.com/maps/place/Chifeng+St,+Datong+District,+Taipei+City,+Taiwan+103/@25.0553262,121.5170477,17z/data=!3m1!4b1!4m6!3m5!1s0x3442a96bd3b19f4d:0xcc152711989c37f8!8m2!3d25.0553262!4d121.519628!16s%2Fg%2F1tgntx_9?entry=ttu&amp;g_ep=EgoyMDI2MDMxMS4wIKXMDSoASAFQAw%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -741,11 +762,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F704CC38-5C9F-9D4A-8E59-015FB6C6AECA}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="43.5" customWidth="1"/>
-    <col min="3" max="3" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.1640625" customWidth="1"/>
     <col min="4" max="4" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -768,537 +789,593 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>5</v>
+        <v>93</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>17</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="C8" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>26</v>
-      </c>
       <c r="C13" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="C15" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>89</v>
+        <v>29</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="C20" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F20" s="1"/>
       <c r="H20" s="1"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="C21" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F21" s="1"/>
       <c r="H21" s="1"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F22" s="1"/>
       <c r="H22" s="1"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F23" s="1"/>
       <c r="H23" s="1"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F24" s="1"/>
       <c r="H24" s="1"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>89</v>
+        <v>45</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F25" s="1"/>
       <c r="H25" s="1"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>89</v>
+        <v>47</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E34" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E35" t="s">
         <v>90</v>
       </c>
-      <c r="E35" t="s">
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E36" t="s">
         <v>94</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E37" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E38" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1314,5 +1391,6 @@
     <hyperlink ref="E33" r:id="rId9" xr:uid="{90DABBA6-E718-C34D-9990-7C41BCA25C70}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>